--- a/Ore-GradeDeclineConstants.xlsx
+++ b/Ore-GradeDeclineConstants.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Metal</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>CME</t>
+  </si>
+  <si>
+    <t>k</t>
   </si>
   <si>
     <t>Aluminium</t>
@@ -548,12 +551,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -678,7 +696,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -690,34 +708,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -802,7 +820,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -816,11 +834,23 @@
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1328,13 +1358,16 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customHeight="1" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4">
         <v>-1.35</v>
@@ -1348,14 +1381,17 @@
       <c r="F2" s="6">
         <v>1040000000000</v>
       </c>
+      <c r="G2" s="7">
+        <v>1041</v>
+      </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customHeight="1" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>-2.06</v>
@@ -1369,14 +1405,17 @@
       <c r="F3" s="6">
         <v>6790000000</v>
       </c>
+      <c r="G3" s="8">
+        <v>40</v>
+      </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" customHeight="1" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4">
         <v>-1.15</v>
@@ -1390,14 +1429,17 @@
       <c r="F4" s="6">
         <v>206000000000</v>
       </c>
+      <c r="G4" s="7">
+        <v>18</v>
+      </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customHeight="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4">
         <v>-4.86</v>
@@ -1411,35 +1453,39 @@
       <c r="F5" s="6">
         <v>2280000000</v>
       </c>
+      <c r="G5" s="9"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7">
+      <c r="B6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="10">
         <v>-3.61</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="10">
         <v>0.17</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>4360000000000</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>592000000000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>170</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customHeight="1" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4">
         <v>-11.9</v>
@@ -1453,35 +1499,41 @@
       <c r="F7" s="6">
         <v>144000000</v>
       </c>
+      <c r="G7" s="12">
+        <v>2135879</v>
+      </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="9">
+      <c r="B8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="13">
         <v>-0.57</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="13">
         <v>0.13</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="14">
         <v>6460000000000000</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="14">
         <v>34100000000000</v>
+      </c>
+      <c r="G8" s="7">
+        <v>78</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customHeight="1" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4">
         <v>-2.61</v>
@@ -1495,14 +1547,17 @@
       <c r="F9" s="6">
         <v>235000000000</v>
       </c>
+      <c r="G9" s="7">
+        <v>21</v>
+      </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customHeight="1" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4">
         <v>-4.95</v>
@@ -1516,14 +1571,17 @@
       <c r="F10" s="6">
         <v>9810000000</v>
       </c>
+      <c r="G10" s="7">
+        <v>88</v>
+      </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customHeight="1" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4">
         <v>-1.19</v>
@@ -1537,14 +1595,17 @@
       <c r="F11" s="6">
         <v>580000000000</v>
       </c>
+      <c r="G11" s="7">
+        <v>8</v>
+      </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customHeight="1" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="4">
         <v>-6.43</v>
@@ -1558,14 +1619,17 @@
       <c r="F12" s="6">
         <v>6620000000</v>
       </c>
+      <c r="G12" s="7">
+        <v>660</v>
+      </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customHeight="1" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="4">
         <v>-4.26</v>
@@ -1579,14 +1643,17 @@
       <c r="F13" s="6">
         <v>55300000000</v>
       </c>
+      <c r="G13" s="7">
+        <v>136</v>
+      </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="4">
         <v>-4.39</v>
@@ -1600,14 +1667,15 @@
       <c r="F14" s="6">
         <v>1070000000</v>
       </c>
+      <c r="G14" s="9"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4">
         <v>-2.14</v>
@@ -1621,14 +1689,17 @@
       <c r="F15" s="6">
         <v>978000000000</v>
       </c>
+      <c r="G15" s="7">
+        <v>29</v>
+      </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customHeight="1" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="4">
         <v>-8.08</v>
@@ -1642,14 +1713,17 @@
       <c r="F16" s="6">
         <v>1130000000</v>
       </c>
+      <c r="G16" s="7">
+        <v>8813</v>
+      </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customHeight="1" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4">
         <v>-4.95</v>
@@ -1663,14 +1737,17 @@
       <c r="F17" s="6">
         <v>20000000000</v>
       </c>
+      <c r="G17" s="8">
+        <v>133</v>
+      </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customHeight="1" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="4">
         <v>-5.54</v>
@@ -1684,14 +1761,17 @@
       <c r="F18" s="6">
         <v>2710000000</v>
       </c>
+      <c r="G18" s="7">
+        <v>3697</v>
+      </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customHeight="1" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" s="4">
         <v>-1.62</v>
@@ -1704,6 +1784,9 @@
       </c>
       <c r="F19" s="6">
         <v>458000000000</v>
+      </c>
+      <c r="G19" s="7">
+        <v>13</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -1723,7 +1806,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:2">

--- a/Ore-GradeDeclineConstants.xlsx
+++ b/Ore-GradeDeclineConstants.xlsx
@@ -105,7 +105,7 @@
     <t>Li</t>
   </si>
   <si>
-    <t xml:space="preserve">Manganese </t>
+    <t>Manganese</t>
   </si>
   <si>
     <t>Mn</t>
